--- a/wooclap/imports/07_Intro_ML_Part_1.xlsx
+++ b/wooclap/imports/07_Intro_ML_Part_1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$5</definedName>

--- a/wooclap/imports/07_Intro_ML_Part_1.xlsx
+++ b/wooclap/imports/07_Intro_ML_Part_1.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L03-C01 · An app is shown many photos marked “cat” or “dog”. It then labels a new photo. Which part is learning from examples?</t>
+          <t>L03-C01 · A crop model predicts a new field’s yield without changing its parameters. Later, an optimizer updates those parameters using the measured yield. How should we describe these two stages?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Displaying the app’s logo.</t>
+          <t>Both are inference because the model family stays unchanged.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Saving the new photo’s file name.</t>
+          <t>Both are training because both stages use data.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Simply opening the app on a phone.</t>
+          <t>The prediction is training; the later parameter update is inference.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Using the marked photos to adjust how it recognizes cats and dogs.</t>
+          <t>The fixed-model prediction is inference; the parameter update is training.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L03-C02 · You want to teach a computer to tell cats from dogs using examples. Which training collection gives it the most useful feedback?</t>
+          <t>L03-C02 · One dataset records plant species as codes {0,1,2}; another records crop yield in kg. Both targets are numbers. Which task choice follows from what those targets mean?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Photos paired only with random file names.</t>
+          <t>Regression for both, because both targets are stored as numbers.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Photos paired with the correct “cat” or “dog” label.</t>
+          <t>Classification for species; regression for yield.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>A list of camera prices with no animal photos.</t>
+          <t>Regression for species; classification for yield, because yield was measured.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Only the words “cat” and “dog”, with no examples.</t>
+          <t>Classification for both, because each training example has a known target.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>L03-C03 · We hide one word from an existing sentence and ask a model to guess it. Where can we find the correct answer?</t>
+          <t>L03-C03 · The recorded sentence is “The crop needs water”. We hide “water”; a model predicts the plausible word “sunlight”. Which statement about this self-supervised training pair is correct?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>In the original sentence before the word was hidden.</t>
+          <t>“Water” is the target; a plausible alternative can still disagree with this recorded target.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Only by asking someone to write an entirely new sentence.</t>
+          <t>“Sunlight” becomes the target because the model predicted it.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>In the model’s guess, which must always be right.</t>
+          <t>Any plausible word automatically counts as the recorded correct target.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Nowhere: hiding a word removes all possibility of checking it.</t>
+          <t>A person must annotate a new target because the original word was hidden.</t>
         </is>
       </c>
       <c r="H4" s="2" t="n"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>L03-C04 · You usually choose a restaurant you like. Why might you try a new one?</t>
+          <t>L03-C04 · A bandit arm A rewarded 6 of 10 pulls, B rewarded 1 of 2, and C rewarded 0 of 1. Rewards are noisy. A rule now always picks A and never samples the other arms. What can go wrong?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Because a new restaurant is guaranteed to be better.</t>
+          <t>The 6/10 rate establishes A’s true reward probability exactly, so no better arm can be missed.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>To learn whether it might be even better.</t>
+          <t>Early noisy results may hide a better arm; occasionally sampling other arms can reveal it.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Because trying something new guarantees a good meal.</t>
+          <t>C’s one zero reward proves that it cannot be the best arm.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Because previous experience tells you exactly how every new restaurant tastes.</t>
+          <t>Trying B instead guarantees a larger reward on the very next pull.</t>
         </is>
       </c>
       <c r="H5" s="3" t="n"/>
